--- a/data/evaluation/gold_dataset_for_llm_generation.xlsx
+++ b/data/evaluation/gold_dataset_for_llm_generation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samil/Desktop/ITSkillsSprintProjects/banking-regulatory-intelligence-platform/data/evaluation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7FC974-DCC3-42BB-BE8B-889C03B7FF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72515AC2-42FC-E349-AC5D-BB7C44F34BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA94A989-87D8-487D-A72D-4BC2D6F986A4}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{CA94A989-87D8-487D-A72D-4BC2D6F986A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3228,7 +3228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3241,10 +3241,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3270,9 +3266,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3310,7 +3306,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3416,7 +3412,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3558,7 +3554,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3567,18 +3563,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C8BE05-B6B6-44AC-9428-CFFFFD422F72}">
   <dimension ref="A1:G238"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="68.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3601,7 +3597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3624,7 +3620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -3647,7 +3643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -3670,7 +3666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="112" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -3693,7 +3689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -3716,7 +3712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="112" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -3739,7 +3735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="112" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -3762,7 +3758,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -3785,7 +3781,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="112" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -3808,7 +3804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="96" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -3827,11 +3823,11 @@
       <c r="F11" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="96" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
@@ -3854,7 +3850,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="112" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>47</v>
       </c>
@@ -3877,7 +3873,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>48</v>
       </c>
@@ -3900,7 +3896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
@@ -3923,7 +3919,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3946,7 +3942,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>51</v>
       </c>
@@ -3965,11 +3961,11 @@
       <c r="F17" s="2">
         <v>27.1</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
@@ -3988,11 +3984,11 @@
       <c r="F18" s="2">
         <v>27.2</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>58</v>
       </c>
@@ -4015,7 +4011,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="96" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
@@ -4038,7 +4034,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="96" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>60</v>
       </c>
@@ -4061,7 +4057,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>62</v>
       </c>
@@ -4084,7 +4080,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="112" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>65</v>
       </c>
@@ -4107,7 +4103,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>68</v>
       </c>
@@ -4130,7 +4126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>71</v>
       </c>
@@ -4153,7 +4149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>74</v>
       </c>
@@ -4176,7 +4172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="64" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>78</v>
       </c>
@@ -4199,7 +4195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="112" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>82</v>
       </c>
@@ -4222,7 +4218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>86</v>
       </c>
@@ -4245,7 +4241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>89</v>
       </c>
@@ -4268,7 +4264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="96" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>92</v>
       </c>
@@ -4291,7 +4287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="80" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>95</v>
       </c>
@@ -4314,8 +4310,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -4337,8 +4333,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -4360,8 +4356,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -4383,8 +4379,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -4406,8 +4402,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -4429,8 +4425,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -4452,8 +4448,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -4475,8 +4471,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
+    <row r="40" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -4498,8 +4494,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -4521,11 +4517,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
+    <row r="42" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -4544,11 +4540,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -4567,11 +4563,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+    <row r="44" spans="1:7" ht="144" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -4590,11 +4586,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+    <row r="45" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -4613,11 +4609,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -4636,11 +4632,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
+    <row r="47" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -4659,11 +4655,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+    <row r="48" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -4682,11 +4678,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+    <row r="49" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -4705,11 +4701,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
+    <row r="50" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -4728,11 +4724,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
+    <row r="51" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -4751,11 +4747,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
+    <row r="52" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -4774,11 +4770,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
+    <row r="53" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -4797,11 +4793,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
+    <row r="54" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -4820,11 +4816,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
+    <row r="55" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -4843,11 +4839,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
+    <row r="56" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -4866,11 +4862,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
+    <row r="57" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -4889,11 +4885,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
+    <row r="58" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -4912,11 +4908,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
+    <row r="59" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -4935,11 +4931,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
+    <row r="60" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -4958,11 +4954,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
+    <row r="61" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C61" s="2" t="s">
@@ -4981,11 +4977,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
+    <row r="62" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -5004,11 +5000,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
+    <row r="63" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C63" s="2" t="s">
@@ -5027,11 +5023,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
+    <row r="64" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -5050,11 +5046,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
+    <row r="65" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -5073,11 +5069,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
+    <row r="66" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -5096,11 +5092,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
+    <row r="67" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -5119,11 +5115,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
+    <row r="68" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -5142,11 +5138,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
+    <row r="69" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -5165,11 +5161,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
+    <row r="70" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C70" s="2" t="s">
@@ -5188,11 +5184,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
+    <row r="71" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C71" s="2" t="s">
@@ -5211,11 +5207,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
+    <row r="72" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C72" s="2" t="s">
@@ -5234,11 +5230,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
+    <row r="73" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C73" s="2" t="s">
@@ -5257,11 +5253,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
+    <row r="74" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C74" s="2" t="s">
@@ -5280,11 +5276,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
+    <row r="75" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C75" s="2" t="s">
@@ -5303,11 +5299,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
+    <row r="76" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C76" s="2" t="s">
@@ -5326,11 +5322,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
+    <row r="77" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C77" s="2" t="s">
@@ -5349,14 +5345,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
+    <row r="78" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="2" t="s">
         <v>305</v>
       </c>
       <c r="D78" s="2" t="s">
@@ -5372,14 +5368,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="s">
+    <row r="79" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="2" t="s">
         <v>309</v>
       </c>
       <c r="D79" s="2" t="s">
@@ -5395,14 +5391,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
+    <row r="80" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="2" t="s">
         <v>313</v>
       </c>
       <c r="D80" s="2" t="s">
@@ -5418,14 +5414,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
+    <row r="81" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="2" t="s">
         <v>317</v>
       </c>
       <c r="D81" s="2" t="s">
@@ -5441,14 +5437,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
+    <row r="82" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="2" t="s">
         <v>320</v>
       </c>
       <c r="D82" s="2" t="s">
@@ -5464,11 +5460,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
+    <row r="83" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C83" s="2" t="s">
@@ -5487,11 +5483,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
+    <row r="84" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C84" s="2" t="s">
@@ -5510,11 +5506,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
+    <row r="85" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C85" s="2" t="s">
@@ -5533,11 +5529,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
+    <row r="86" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C86" s="2" t="s">
@@ -5556,11 +5552,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
+    <row r="87" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A87" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C87" s="2" t="s">
@@ -5579,11 +5575,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
+    <row r="88" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C88" s="2" t="s">
@@ -5602,11 +5598,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
+    <row r="89" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C89" s="2" t="s">
@@ -5625,11 +5621,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
+    <row r="90" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C90" s="2" t="s">
@@ -5648,11 +5644,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
+    <row r="91" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A91" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C91" s="2" t="s">
@@ -5671,11 +5667,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
+    <row r="92" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C92" s="2" t="s">
@@ -5694,11 +5690,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
+    <row r="93" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C93" s="2" t="s">
@@ -5717,11 +5713,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
+    <row r="94" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C94" s="2" t="s">
@@ -5740,11 +5736,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
+    <row r="95" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="B95" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C95" s="2" t="s">
@@ -5763,11 +5759,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
+    <row r="96" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C96" s="2" t="s">
@@ -5786,11 +5782,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
+    <row r="97" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C97" s="2" t="s">
@@ -5809,3246 +5805,3246 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A98" s="7" t="s">
+    <row r="98" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A98" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C98" s="8" t="s">
+      <c r="C98" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="D98" s="8" t="s">
+      <c r="D98" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="E98" s="7" t="s">
+      <c r="E98" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="F98" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="G98" s="7">
+      <c r="G98" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A99" s="7" t="s">
+    <row r="99" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A99" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="D99" s="8" t="s">
+      <c r="D99" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="E99" s="7" t="s">
+      <c r="E99" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="F99" s="7" t="s">
+      <c r="F99" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="G99" s="7">
+      <c r="G99" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A100" s="7" t="s">
+    <row r="100" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A100" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="D100" s="8" t="s">
+      <c r="D100" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="E100" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="F100" s="7" t="s">
+      <c r="F100" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="G100" s="7">
+      <c r="G100" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A101" s="7" t="s">
+    <row r="101" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="D101" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="E101" s="7" t="s">
+      <c r="E101" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="F101" s="7" t="s">
+      <c r="F101" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="G101" s="7">
+      <c r="G101" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A102" s="7" t="s">
+    <row r="102" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C102" s="8" t="s">
+      <c r="C102" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="D102" s="8" t="s">
+      <c r="D102" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E102" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="F102" s="7" t="s">
+      <c r="F102" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="G102" s="7">
+      <c r="G102" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A103" s="7" t="s">
+    <row r="103" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A103" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="D103" s="8" t="s">
+      <c r="D103" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E103" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="F103" s="7" t="s">
+      <c r="F103" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="G103" s="7">
+      <c r="G103" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A104" s="7" t="s">
+    <row r="104" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A104" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="D104" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="E104" s="7" t="s">
+      <c r="E104" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="F104" s="7" t="s">
+      <c r="F104" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="G104" s="7">
+      <c r="G104" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A105" s="7" t="s">
+    <row r="105" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A105" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="D105" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="E105" s="7" t="s">
+      <c r="E105" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="F105" s="7" t="s">
+      <c r="F105" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="G105" s="7">
+      <c r="G105" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A106" s="7" t="s">
+    <row r="106" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="D106" s="8" t="s">
+      <c r="D106" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="E106" s="7" t="s">
+      <c r="E106" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="F106" s="7" t="s">
+      <c r="F106" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="G106" s="7">
+      <c r="G106" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A107" s="7" t="s">
+    <row r="107" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A107" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="D107" s="8" t="s">
+      <c r="D107" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="E107" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="F107" s="7" t="s">
+      <c r="F107" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="G107" s="7">
+      <c r="G107" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A108" s="7" t="s">
+    <row r="108" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C108" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="D108" s="8" t="s">
+      <c r="D108" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="E108" s="7" t="s">
+      <c r="E108" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="F108" s="7" t="s">
+      <c r="F108" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="G108" s="7">
+      <c r="G108" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A109" s="7" t="s">
+    <row r="109" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A109" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C109" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="D109" s="8" t="s">
+      <c r="D109" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="E109" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="F109" s="7" t="s">
+      <c r="F109" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="G109" s="7">
+      <c r="G109" s="5">
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A110" s="7" t="s">
+    <row r="110" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A110" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="C110" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="D110" s="8" t="s">
+      <c r="D110" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="E110" s="7" t="s">
+      <c r="E110" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="F110" s="7" t="s">
+      <c r="F110" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="G110" s="7">
+      <c r="G110" s="5">
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A111" s="7" t="s">
+    <row r="111" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A111" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="C111" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="D111" s="8" t="s">
+      <c r="D111" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="E111" s="7" t="s">
+      <c r="E111" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="F111" s="7" t="s">
+      <c r="F111" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="G111" s="7">
+      <c r="G111" s="5">
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A112" s="7" t="s">
+    <row r="112" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A112" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C112" s="8" t="s">
+      <c r="C112" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="D112" s="8" t="s">
+      <c r="D112" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="E112" s="7" t="s">
+      <c r="E112" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="F112" s="7" t="s">
+      <c r="F112" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="G112" s="7">
+      <c r="G112" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A113" s="7" t="s">
+    <row r="113" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A113" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C113" s="8" t="s">
+      <c r="C113" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="D113" s="8" t="s">
+      <c r="D113" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="E113" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="F113" s="7" t="s">
+      <c r="F113" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="G113" s="7">
+      <c r="G113" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A114" s="7" t="s">
+    <row r="114" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A114" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C114" s="8" t="s">
+      <c r="C114" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="D114" s="8" t="s">
+      <c r="D114" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="E114" s="7" t="s">
+      <c r="E114" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="F114" s="7" t="s">
+      <c r="F114" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="G114" s="7">
+      <c r="G114" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A115" s="7" t="s">
+    <row r="115" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A115" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="D115" s="8" t="s">
+      <c r="D115" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="E115" s="7" t="s">
+      <c r="E115" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="F115" s="7" t="s">
+      <c r="F115" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="G115" s="7">
+      <c r="G115" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A116" s="7" t="s">
+    <row r="116" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A116" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C116" s="8" t="s">
+      <c r="C116" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="D116" s="8" t="s">
+      <c r="D116" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="E116" s="7" t="s">
+      <c r="E116" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="F116" s="7" t="s">
+      <c r="F116" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="G116" s="7">
+      <c r="G116" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A117" s="7" t="s">
+    <row r="117" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A117" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="D117" s="8" t="s">
+      <c r="D117" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="E117" s="7" t="s">
+      <c r="E117" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="F117" s="7" t="s">
+      <c r="F117" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="G117" s="7">
+      <c r="G117" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A118" s="7" t="s">
+    <row r="118" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A118" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C118" s="8" t="s">
+      <c r="C118" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="D118" s="8" t="s">
+      <c r="D118" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="E118" s="7" t="s">
+      <c r="E118" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="F118" s="7" t="s">
+      <c r="F118" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="G118" s="7">
+      <c r="G118" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A119" s="7" t="s">
+    <row r="119" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A119" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="B119" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="D119" s="8" t="s">
+      <c r="D119" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="E119" s="7" t="s">
+      <c r="E119" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="F119" s="7" t="s">
+      <c r="F119" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="G119" s="7">
+      <c r="G119" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A120" s="7" t="s">
+    <row r="120" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A120" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="B120" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C120" s="8" t="s">
+      <c r="C120" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="D120" s="8" t="s">
+      <c r="D120" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="E120" s="7" t="s">
+      <c r="E120" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="F120" s="7" t="s">
+      <c r="F120" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="G120" s="7">
+      <c r="G120" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A121" s="7" t="s">
+    <row r="121" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A121" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="B121" s="7" t="s">
+      <c r="B121" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="D121" s="8" t="s">
+      <c r="D121" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="E121" s="7" t="s">
+      <c r="E121" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="F121" s="7" t="s">
+      <c r="F121" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G121" s="7">
+      <c r="G121" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A122" s="7" t="s">
+    <row r="122" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A122" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B122" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C122" s="8" t="s">
+      <c r="C122" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D122" s="8" t="s">
+      <c r="D122" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="E122" s="7" t="s">
+      <c r="E122" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="F122" s="7" t="s">
+      <c r="F122" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G122" s="7">
+      <c r="G122" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A123" s="7" t="s">
+    <row r="123" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A123" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="B123" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="D123" s="8" t="s">
+      <c r="D123" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="E123" s="7" t="s">
+      <c r="E123" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="F123" s="7" t="s">
+      <c r="F123" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="G123" s="7">
+      <c r="G123" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="7" t="s">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A124" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="B124" s="7" t="s">
+      <c r="B124" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C124" s="8" t="s">
+      <c r="C124" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="D124" s="8" t="s">
+      <c r="D124" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="E124" s="7" t="s">
+      <c r="E124" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="F124" s="7" t="s">
+      <c r="F124" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="G124" s="7">
+      <c r="G124" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A125" s="7" t="s">
+    <row r="125" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A125" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="B125" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="D125" s="8" t="s">
+      <c r="D125" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="E125" s="7" t="s">
+      <c r="E125" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="F125" s="7" t="s">
+      <c r="F125" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="G125" s="7">
+      <c r="G125" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A126" s="7" t="s">
+    <row r="126" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A126" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B126" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="D126" s="8" t="s">
+      <c r="D126" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="E126" s="7" t="s">
+      <c r="E126" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="F126" s="7" t="s">
+      <c r="F126" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="G126" s="7">
+      <c r="G126" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A127" s="7" t="s">
+    <row r="127" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A127" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="B127" s="7" t="s">
+      <c r="B127" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="D127" s="8" t="s">
+      <c r="D127" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="E127" s="7" t="s">
+      <c r="E127" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="F127" s="7" t="s">
+      <c r="F127" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="G127" s="7">
+      <c r="G127" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A128" s="7" t="s">
+    <row r="128" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A128" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="B128" s="7" t="s">
+      <c r="B128" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="D128" s="8" t="s">
+      <c r="D128" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="E128" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="F128" s="7" t="s">
+      <c r="F128" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="G128" s="7">
+      <c r="G128" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A129" s="7" t="s">
+    <row r="129" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A129" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="B129" s="7" t="s">
+      <c r="B129" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="D129" s="8" t="s">
+      <c r="D129" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="E129" s="7" t="s">
+      <c r="E129" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="F129" s="7" t="s">
+      <c r="F129" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="G129" s="7">
+      <c r="G129" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A130" s="7" t="s">
+    <row r="130" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A130" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="B130" s="7" t="s">
+      <c r="B130" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="D130" s="8" t="s">
+      <c r="D130" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="E130" s="7" t="s">
+      <c r="E130" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="F130" s="7" t="s">
+      <c r="F130" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="G130" s="7">
+      <c r="G130" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A131" s="7" t="s">
+    <row r="131" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A131" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="B131" s="7" t="s">
+      <c r="B131" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="D131" s="8" t="s">
+      <c r="D131" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="E131" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="F131" s="7" t="s">
+      <c r="F131" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="G131" s="7">
+      <c r="G131" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A132" s="7" t="s">
+    <row r="132" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A132" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="B132" s="7" t="s">
+      <c r="B132" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="D132" s="8" t="s">
+      <c r="D132" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="E132" s="7" t="s">
+      <c r="E132" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="F132" s="7" t="s">
+      <c r="F132" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="G132" s="7">
+      <c r="G132" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A133" s="7" t="s">
+    <row r="133" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A133" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="B133" s="7" t="s">
+      <c r="B133" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="D133" s="8" t="s">
+      <c r="D133" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="E133" s="7" t="s">
+      <c r="E133" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="F133" s="7" t="s">
+      <c r="F133" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="G133" s="7">
+      <c r="G133" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A134" s="7" t="s">
+    <row r="134" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A134" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="B134" s="7" t="s">
+      <c r="B134" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="D134" s="8" t="s">
+      <c r="D134" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="E134" s="7" t="s">
+      <c r="E134" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="F134" s="7" t="s">
+      <c r="F134" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="G134" s="7">
+      <c r="G134" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A135" s="7" t="s">
+    <row r="135" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A135" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="B135" s="7" t="s">
+      <c r="B135" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="D135" s="8" t="s">
+      <c r="D135" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="E135" s="7" t="s">
+      <c r="E135" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="F135" s="7" t="s">
+      <c r="F135" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G135" s="7">
+      <c r="G135" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A136" s="7" t="s">
+    <row r="136" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A136" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="B136" s="7" t="s">
+      <c r="B136" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="D136" s="8" t="s">
+      <c r="D136" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="E136" s="7" t="s">
+      <c r="E136" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="F136" s="7" t="s">
+      <c r="F136" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G136" s="7">
+      <c r="G136" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A137" s="7" t="s">
+    <row r="137" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A137" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="B137" s="7" t="s">
+      <c r="B137" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="D137" s="8" t="s">
+      <c r="D137" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="E137" s="7" t="s">
+      <c r="E137" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="F137" s="7" t="s">
+      <c r="F137" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="G137" s="7">
+      <c r="G137" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A138" s="7" t="s">
+    <row r="138" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A138" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="B138" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="D138" s="8" t="s">
+      <c r="D138" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="E138" s="7" t="s">
+      <c r="E138" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="F138" s="7" t="s">
+      <c r="F138" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G138" s="7">
+      <c r="G138" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A139" s="7" t="s">
+    <row r="139" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A139" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="B139" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="D139" s="8" t="s">
+      <c r="D139" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="E139" s="7" t="s">
+      <c r="E139" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="F139" s="7" t="s">
+      <c r="F139" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="G139" s="7">
+      <c r="G139" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A140" s="7" t="s">
+    <row r="140" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A140" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="B140" s="7" t="s">
+      <c r="B140" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="D140" s="8" t="s">
+      <c r="D140" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="E140" s="7" t="s">
+      <c r="E140" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="F140" s="7" t="s">
+      <c r="F140" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="G140" s="7">
+      <c r="G140" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A141" s="7" t="s">
+    <row r="141" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A141" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="B141" s="7" t="s">
+      <c r="B141" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="D141" s="8" t="s">
+      <c r="D141" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="E141" s="7" t="s">
+      <c r="E141" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="F141" s="7" t="s">
+      <c r="F141" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="G141" s="7">
+      <c r="G141" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A142" s="7" t="s">
+    <row r="142" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A142" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="B142" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="D142" s="8" t="s">
+      <c r="D142" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="E142" s="7" t="s">
+      <c r="E142" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="F142" s="7" t="s">
+      <c r="F142" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="G142" s="7">
+      <c r="G142" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A143" s="7" t="s">
+    <row r="143" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A143" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="B143" s="7" t="s">
+      <c r="B143" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="D143" s="8" t="s">
+      <c r="D143" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="E143" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="F143" s="7" t="s">
+      <c r="F143" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="G143" s="7">
+      <c r="G143" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A144" s="7" t="s">
+    <row r="144" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A144" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="B144" s="7" t="s">
+      <c r="B144" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="C144" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="D144" s="8" t="s">
+      <c r="D144" s="6" t="s">
         <v>561</v>
       </c>
-      <c r="E144" s="7" t="s">
+      <c r="E144" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="F144" s="7" t="s">
+      <c r="F144" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="G144" s="7">
+      <c r="G144" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A145" s="7" t="s">
+    <row r="145" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A145" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="B145" s="7" t="s">
+      <c r="B145" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="D145" s="8" t="s">
+      <c r="D145" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="E145" s="7" t="s">
+      <c r="E145" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="F145" s="7" t="s">
+      <c r="F145" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="G145" s="7">
+      <c r="G145" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A146" s="7" t="s">
+    <row r="146" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A146" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B146" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="D146" s="8" t="s">
+      <c r="D146" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="E146" s="7" t="s">
+      <c r="E146" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="F146" s="7" t="s">
+      <c r="F146" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="G146" s="7">
+      <c r="G146" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A147" s="7" t="s">
+    <row r="147" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A147" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="B147" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="D147" s="8" t="s">
+      <c r="D147" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="E147" s="7" t="s">
+      <c r="E147" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="F147" s="7" t="s">
+      <c r="F147" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="G147" s="7">
+      <c r="G147" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A148" s="7" t="s">
+    <row r="148" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A148" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="B148" s="7" t="s">
+      <c r="B148" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="D148" s="8" t="s">
+      <c r="D148" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="E148" s="7" t="s">
+      <c r="E148" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="F148" s="7" t="s">
+      <c r="F148" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="G148" s="7">
+      <c r="G148" s="5">
         <v>14</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A149" s="7" t="s">
+    <row r="149" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A149" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="B149" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C149" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="D149" s="8" t="s">
+      <c r="D149" s="6" t="s">
         <v>579</v>
       </c>
-      <c r="E149" s="7" t="s">
+      <c r="E149" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="F149" s="7" t="s">
+      <c r="F149" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="G149" s="7">
+      <c r="G149" s="5">
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A150" s="7" t="s">
+    <row r="150" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A150" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="D150" s="8" t="s">
+      <c r="D150" s="6" t="s">
         <v>583</v>
       </c>
-      <c r="E150" s="7" t="s">
+      <c r="E150" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="F150" s="7" t="s">
+      <c r="F150" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="G150" s="7">
+      <c r="G150" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A151" s="7" t="s">
+    <row r="151" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A151" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="B151" s="7" t="s">
+      <c r="B151" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="D151" s="8" t="s">
+      <c r="D151" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="E151" s="7" t="s">
+      <c r="E151" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="F151" s="7" t="s">
+      <c r="F151" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="G151" s="7">
+      <c r="G151" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A152" s="7" t="s">
+    <row r="152" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A152" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="B152" s="7" t="s">
+      <c r="B152" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="C152" s="6" t="s">
         <v>591</v>
       </c>
-      <c r="D152" s="8" t="s">
+      <c r="D152" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="E152" s="7" t="s">
+      <c r="E152" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="F152" s="7" t="s">
+      <c r="F152" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="G152" s="7">
+      <c r="G152" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A153" s="7" t="s">
+    <row r="153" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A153" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B153" s="7" t="s">
+      <c r="B153" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="C153" s="8" t="s">
+      <c r="C153" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="D153" s="8" t="s">
+      <c r="D153" s="6" t="s">
         <v>596</v>
       </c>
-      <c r="E153" s="7" t="s">
+      <c r="E153" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="F153" s="7" t="s">
+      <c r="F153" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="G153" s="7">
+      <c r="G153" s="5">
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A154" s="7" t="s">
+    <row r="154" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A154" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B154" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="C154" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="D154" s="8" t="s">
+      <c r="D154" s="6" t="s">
         <v>600</v>
       </c>
-      <c r="E154" s="7" t="s">
+      <c r="E154" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="F154" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="G154" s="7">
+      <c r="G154" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A155" s="7" t="s">
+    <row r="155" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A155" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="B155" s="7" t="s">
+      <c r="B155" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="C155" s="8" t="s">
+      <c r="C155" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="D155" s="8" t="s">
+      <c r="D155" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="E155" s="7" t="s">
+      <c r="E155" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="F155" s="7" t="s">
+      <c r="F155" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="G155" s="7">
+      <c r="G155" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A156" s="7" t="s">
+    <row r="156" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A156" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="B156" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C156" s="8" t="s">
+      <c r="C156" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="D156" s="8" t="s">
+      <c r="D156" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="E156" s="7" t="s">
+      <c r="E156" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="F156" s="7" t="s">
+      <c r="F156" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="G156" s="7">
+      <c r="G156" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A157" s="7" t="s">
+    <row r="157" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A157" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="B157" s="7" t="s">
+      <c r="B157" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C157" s="8" t="s">
+      <c r="C157" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="D157" s="8" t="s">
+      <c r="D157" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="E157" s="7" t="s">
+      <c r="E157" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="F157" s="7" t="s">
+      <c r="F157" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="G157" s="7">
+      <c r="G157" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A158" s="7" t="s">
+    <row r="158" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A158" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="B158" s="7" t="s">
+      <c r="B158" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C158" s="8" t="s">
+      <c r="C158" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="D158" s="8" t="s">
+      <c r="D158" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="E158" s="7" t="s">
+      <c r="E158" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="F158" s="7" t="s">
+      <c r="F158" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="G158" s="7">
+      <c r="G158" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A159" s="7" t="s">
+    <row r="159" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A159" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="B159" s="7" t="s">
+      <c r="B159" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C159" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="D159" s="8" t="s">
+      <c r="D159" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="E159" s="7" t="s">
+      <c r="E159" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="F159" s="7" t="s">
+      <c r="F159" s="5" t="s">
         <v>625</v>
       </c>
-      <c r="G159" s="7">
+      <c r="G159" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A160" s="7" t="s">
+    <row r="160" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A160" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="B160" s="7" t="s">
+      <c r="B160" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C160" s="8" t="s">
+      <c r="C160" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="D160" s="8" t="s">
+      <c r="D160" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="E160" s="7" t="s">
+      <c r="E160" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="F160" s="7" t="s">
+      <c r="F160" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="G160" s="7">
+      <c r="G160" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A161" s="7" t="s">
+    <row r="161" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A161" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="B161" s="7" t="s">
+      <c r="B161" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C161" s="8" t="s">
+      <c r="C161" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="D161" s="8" t="s">
+      <c r="D161" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="E161" s="7" t="s">
+      <c r="E161" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="F161" s="7" t="s">
+      <c r="F161" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="G161" s="7">
+      <c r="G161" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A162" s="7" t="s">
+    <row r="162" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A162" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="B162" s="7" t="s">
+      <c r="B162" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C162" s="8" t="s">
+      <c r="C162" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="D162" s="8" t="s">
+      <c r="D162" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="E162" s="7" t="s">
+      <c r="E162" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="F162" s="7" t="s">
+      <c r="F162" s="5" t="s">
         <v>625</v>
       </c>
-      <c r="G162" s="7">
+      <c r="G162" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A163" s="7" t="s">
+    <row r="163" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A163" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="B163" s="7" t="s">
+      <c r="B163" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C163" s="8" t="s">
+      <c r="C163" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="D163" s="8" t="s">
+      <c r="D163" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="E163" s="7" t="s">
+      <c r="E163" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="F163" s="7" t="s">
+      <c r="F163" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="G163" s="7">
+      <c r="G163" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A164" s="7" t="s">
+    <row r="164" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A164" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="B164" s="7" t="s">
+      <c r="B164" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C164" s="8" t="s">
+      <c r="C164" s="6" t="s">
         <v>642</v>
       </c>
-      <c r="D164" s="8" t="s">
+      <c r="D164" s="6" t="s">
         <v>643</v>
       </c>
-      <c r="E164" s="7" t="s">
+      <c r="E164" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="F164" s="7" t="s">
+      <c r="F164" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="G164" s="7">
+      <c r="G164" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A165" s="7" t="s">
+    <row r="165" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A165" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="B165" s="7" t="s">
+      <c r="B165" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C165" s="8" t="s">
+      <c r="C165" s="6" t="s">
         <v>646</v>
       </c>
-      <c r="D165" s="8" t="s">
+      <c r="D165" s="6" t="s">
         <v>647</v>
       </c>
-      <c r="E165" s="7" t="s">
+      <c r="E165" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="F165" s="7" t="s">
+      <c r="F165" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="G165" s="7">
+      <c r="G165" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A166" s="7" t="s">
+    <row r="166" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A166" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="B166" s="7" t="s">
+      <c r="B166" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C166" s="8" t="s">
+      <c r="C166" s="6" t="s">
         <v>651</v>
       </c>
-      <c r="D166" s="8" t="s">
+      <c r="D166" s="6" t="s">
         <v>652</v>
       </c>
-      <c r="E166" s="7" t="s">
+      <c r="E166" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="F166" s="7" t="s">
+      <c r="F166" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="G166" s="7">
+      <c r="G166" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A167" s="7" t="s">
+    <row r="167" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A167" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="B167" s="7" t="s">
+      <c r="B167" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C167" s="8" t="s">
+      <c r="C167" s="6" t="s">
         <v>655</v>
       </c>
-      <c r="D167" s="8" t="s">
+      <c r="D167" s="6" t="s">
         <v>656</v>
       </c>
-      <c r="E167" s="7" t="s">
+      <c r="E167" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="F167" s="7" t="s">
+      <c r="F167" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="G167" s="7">
+      <c r="G167" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A168" s="7" t="s">
+    <row r="168" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A168" s="5" t="s">
         <v>657</v>
       </c>
-      <c r="B168" s="7" t="s">
+      <c r="B168" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C168" s="8" t="s">
+      <c r="C168" s="6" t="s">
         <v>658</v>
       </c>
-      <c r="D168" s="8" t="s">
+      <c r="D168" s="6" t="s">
         <v>659</v>
       </c>
-      <c r="E168" s="7" t="s">
+      <c r="E168" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="F168" s="7" t="s">
+      <c r="F168" s="5" t="s">
         <v>625</v>
       </c>
-      <c r="G168" s="7">
+      <c r="G168" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A169" s="7" t="s">
+    <row r="169" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A169" s="5" t="s">
         <v>661</v>
       </c>
-      <c r="B169" s="7" t="s">
+      <c r="B169" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C169" s="8" t="s">
+      <c r="C169" s="6" t="s">
         <v>662</v>
       </c>
-      <c r="D169" s="8" t="s">
+      <c r="D169" s="6" t="s">
         <v>663</v>
       </c>
-      <c r="E169" s="7" t="s">
+      <c r="E169" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="F169" s="7" t="s">
+      <c r="F169" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="G169" s="7">
+      <c r="G169" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A170" s="7" t="s">
+    <row r="170" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A170" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="B170" s="7" t="s">
+      <c r="B170" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C170" s="8" t="s">
+      <c r="C170" s="6" t="s">
         <v>666</v>
       </c>
-      <c r="D170" s="8" t="s">
+      <c r="D170" s="6" t="s">
         <v>667</v>
       </c>
-      <c r="E170" s="7" t="s">
+      <c r="E170" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="F170" s="7" t="s">
+      <c r="F170" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="G170" s="7">
+      <c r="G170" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A171" s="7" t="s">
+    <row r="171" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A171" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="B171" s="7" t="s">
+      <c r="B171" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C171" s="8" t="s">
+      <c r="C171" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="D171" s="8" t="s">
+      <c r="D171" s="6" t="s">
         <v>671</v>
       </c>
-      <c r="E171" s="7" t="s">
+      <c r="E171" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="F171" s="7" t="s">
+      <c r="F171" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="G171" s="7">
+      <c r="G171" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A172" s="7" t="s">
+    <row r="172" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A172" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="B172" s="7" t="s">
+      <c r="B172" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C172" s="8" t="s">
+      <c r="C172" s="6" t="s">
         <v>675</v>
       </c>
-      <c r="D172" s="8" t="s">
+      <c r="D172" s="6" t="s">
         <v>676</v>
       </c>
-      <c r="E172" s="7" t="s">
+      <c r="E172" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="F172" s="7" t="s">
+      <c r="F172" s="5" t="s">
         <v>677</v>
       </c>
-      <c r="G172" s="7">
+      <c r="G172" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A173" s="7" t="s">
+    <row r="173" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A173" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="B173" s="7" t="s">
+      <c r="B173" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C173" s="8" t="s">
+      <c r="C173" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="D173" s="8" t="s">
+      <c r="D173" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="E173" s="7" t="s">
+      <c r="E173" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="F173" s="7" t="s">
+      <c r="F173" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="G173" s="7">
+      <c r="G173" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A174" s="7" t="s">
+    <row r="174" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A174" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="B174" s="7" t="s">
+      <c r="B174" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C174" s="8" t="s">
+      <c r="C174" s="6" t="s">
         <v>683</v>
       </c>
-      <c r="D174" s="8" t="s">
+      <c r="D174" s="6" t="s">
         <v>684</v>
       </c>
-      <c r="E174" s="7" t="s">
+      <c r="E174" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="F174" s="7" t="s">
+      <c r="F174" s="5" t="s">
         <v>686</v>
       </c>
-      <c r="G174" s="7">
+      <c r="G174" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A175" s="7" t="s">
+    <row r="175" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A175" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="B175" s="7" t="s">
+      <c r="B175" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C175" s="8" t="s">
+      <c r="C175" s="6" t="s">
         <v>688</v>
       </c>
-      <c r="D175" s="8" t="s">
+      <c r="D175" s="6" t="s">
         <v>689</v>
       </c>
-      <c r="E175" s="7" t="s">
+      <c r="E175" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="F175" s="7" t="s">
+      <c r="F175" s="5" t="s">
         <v>686</v>
       </c>
-      <c r="G175" s="7">
+      <c r="G175" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A176" s="7" t="s">
+    <row r="176" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A176" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B176" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="C176" s="8" t="s">
+      <c r="C176" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="D176" s="8" t="s">
+      <c r="D176" s="6" t="s">
         <v>692</v>
       </c>
-      <c r="E176" s="7" t="s">
+      <c r="E176" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="F176" s="7" t="s">
+      <c r="F176" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="G176" s="7">
+      <c r="G176" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A177" s="7" t="s">
+    <row r="177" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A177" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="B177" s="7" t="s">
+      <c r="B177" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C177" s="8" t="s">
+      <c r="C177" s="6" t="s">
         <v>696</v>
       </c>
-      <c r="D177" s="8" t="s">
+      <c r="D177" s="6" t="s">
         <v>697</v>
       </c>
-      <c r="E177" s="7" t="s">
+      <c r="E177" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="F177" s="7" t="s">
+      <c r="F177" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="G177" s="7">
+      <c r="G177" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A178" s="7" t="s">
+    <row r="178" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A178" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="B178" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C178" s="8" t="s">
+      <c r="C178" s="6" t="s">
         <v>700</v>
       </c>
-      <c r="D178" s="8" t="s">
+      <c r="D178" s="6" t="s">
         <v>701</v>
       </c>
-      <c r="E178" s="7" t="s">
+      <c r="E178" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="F178" s="7" t="s">
+      <c r="F178" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="G178" s="7">
+      <c r="G178" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A179" s="7" t="s">
+    <row r="179" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A179" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="B179" s="7" t="s">
+      <c r="B179" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C179" s="8" t="s">
+      <c r="C179" s="6" t="s">
         <v>703</v>
       </c>
-      <c r="D179" s="8" t="s">
+      <c r="D179" s="6" t="s">
         <v>704</v>
       </c>
-      <c r="E179" s="7" t="s">
+      <c r="E179" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="F179" s="7" t="s">
+      <c r="F179" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="G179" s="7">
+      <c r="G179" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A180" s="7" t="s">
+    <row r="180" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A180" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="B180" s="7" t="s">
+      <c r="B180" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C180" s="8" t="s">
+      <c r="C180" s="6" t="s">
         <v>706</v>
       </c>
-      <c r="D180" s="8" t="s">
+      <c r="D180" s="6" t="s">
         <v>707</v>
       </c>
-      <c r="E180" s="7" t="s">
+      <c r="E180" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="F180" s="7" t="s">
+      <c r="F180" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="G180" s="7">
+      <c r="G180" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A181" s="7" t="s">
+    <row r="181" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A181" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="B181" s="7" t="s">
+      <c r="B181" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C181" s="8" t="s">
+      <c r="C181" s="6" t="s">
         <v>710</v>
       </c>
-      <c r="D181" s="8" t="s">
+      <c r="D181" s="6" t="s">
         <v>711</v>
       </c>
-      <c r="E181" s="7" t="s">
+      <c r="E181" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="F181" s="7" t="s">
+      <c r="F181" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="G181" s="7">
+      <c r="G181" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A182" s="7" t="s">
+    <row r="182" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A182" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="B182" s="7" t="s">
+      <c r="B182" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C182" s="8" t="s">
+      <c r="C182" s="6" t="s">
         <v>713</v>
       </c>
-      <c r="D182" s="8" t="s">
+      <c r="D182" s="6" t="s">
         <v>714</v>
       </c>
-      <c r="E182" s="7" t="s">
+      <c r="E182" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="F182" s="7" t="s">
+      <c r="F182" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="G182" s="7">
+      <c r="G182" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A183" s="7" t="s">
+    <row r="183" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A183" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="B183" s="7" t="s">
+      <c r="B183" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C183" s="8" t="s">
+      <c r="C183" s="6" t="s">
         <v>716</v>
       </c>
-      <c r="D183" s="8" t="s">
+      <c r="D183" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="E183" s="7" t="s">
+      <c r="E183" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="F183" s="7" t="s">
+      <c r="F183" s="5" t="s">
         <v>625</v>
       </c>
-      <c r="G183" s="7">
+      <c r="G183" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A184" s="7" t="s">
+    <row r="184" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A184" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="B184" s="7" t="s">
+      <c r="B184" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C184" s="8" t="s">
+      <c r="C184" s="6" t="s">
         <v>720</v>
       </c>
-      <c r="D184" s="8" t="s">
+      <c r="D184" s="6" t="s">
         <v>721</v>
       </c>
-      <c r="E184" s="7" t="s">
+      <c r="E184" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="F184" s="7" t="s">
+      <c r="F184" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="G184" s="7">
+      <c r="G184" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A185" s="7" t="s">
+    <row r="185" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A185" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="B185" s="7" t="s">
+      <c r="B185" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C185" s="8" t="s">
+      <c r="C185" s="6" t="s">
         <v>724</v>
       </c>
-      <c r="D185" s="8" t="s">
+      <c r="D185" s="6" t="s">
         <v>725</v>
       </c>
-      <c r="E185" s="7" t="s">
+      <c r="E185" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="F185" s="7" t="s">
+      <c r="F185" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="G185" s="7">
+      <c r="G185" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A186" s="7" t="s">
+    <row r="186" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A186" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="B186" s="7" t="s">
+      <c r="B186" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C186" s="8" t="s">
+      <c r="C186" s="6" t="s">
         <v>727</v>
       </c>
-      <c r="D186" s="8" t="s">
+      <c r="D186" s="6" t="s">
         <v>728</v>
       </c>
-      <c r="E186" s="7" t="s">
+      <c r="E186" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="F186" s="7" t="s">
+      <c r="F186" s="5" t="s">
         <v>729</v>
       </c>
-      <c r="G186" s="7">
+      <c r="G186" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A187" s="7" t="s">
+    <row r="187" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A187" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="B187" s="7" t="s">
+      <c r="B187" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C187" s="8" t="s">
+      <c r="C187" s="6" t="s">
         <v>731</v>
       </c>
-      <c r="D187" s="8" t="s">
+      <c r="D187" s="6" t="s">
         <v>732</v>
       </c>
-      <c r="E187" s="7" t="s">
+      <c r="E187" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="F187" s="7" t="s">
+      <c r="F187" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="G187" s="7">
+      <c r="G187" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A188" s="7" t="s">
+    <row r="188" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A188" s="5" t="s">
         <v>734</v>
       </c>
-      <c r="B188" s="7" t="s">
+      <c r="B188" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C188" s="8" t="s">
+      <c r="C188" s="6" t="s">
         <v>735</v>
       </c>
-      <c r="D188" s="8" t="s">
+      <c r="D188" s="6" t="s">
         <v>736</v>
       </c>
-      <c r="E188" s="7" t="s">
+      <c r="E188" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="F188" s="7" t="s">
+      <c r="F188" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="G188" s="7">
+      <c r="G188" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A189" s="7" t="s">
+    <row r="189" spans="1:7" ht="84" x14ac:dyDescent="0.2">
+      <c r="A189" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="B189" s="7" t="s">
+      <c r="B189" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C189" s="8" t="s">
+      <c r="C189" s="6" t="s">
         <v>739</v>
       </c>
-      <c r="D189" s="8" t="s">
+      <c r="D189" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="E189" s="7" t="s">
+      <c r="E189" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="F189" s="7" t="s">
+      <c r="F189" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="G189" s="7">
+      <c r="G189" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A190" s="7" t="s">
+    <row r="190" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A190" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="B190" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C190" s="8" t="s">
+      <c r="C190" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="D190" s="8" t="s">
+      <c r="D190" s="6" t="s">
         <v>743</v>
       </c>
-      <c r="E190" s="7" t="s">
+      <c r="E190" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="F190" s="7" t="s">
+      <c r="F190" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="G190" s="7">
+      <c r="G190" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A191" s="7" t="s">
+    <row r="191" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A191" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C191" s="8" t="s">
+      <c r="C191" s="6" t="s">
         <v>746</v>
       </c>
-      <c r="D191" s="8" t="s">
+      <c r="D191" s="6" t="s">
         <v>747</v>
       </c>
-      <c r="E191" s="7" t="s">
+      <c r="E191" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F191" s="7" t="s">
+      <c r="F191" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="G191" s="7">
+      <c r="G191" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A192" s="7" t="s">
+    <row r="192" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A192" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="B192" s="7" t="s">
+      <c r="B192" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C192" s="8" t="s">
+      <c r="C192" s="6" t="s">
         <v>750</v>
       </c>
-      <c r="D192" s="8" t="s">
+      <c r="D192" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="E192" s="7" t="s">
+      <c r="E192" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F192" s="7" t="s">
+      <c r="F192" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="G192" s="7">
+      <c r="G192" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A193" s="7" t="s">
+    <row r="193" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A193" s="5" t="s">
         <v>752</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B193" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C193" s="8" t="s">
+      <c r="C193" s="6" t="s">
         <v>753</v>
       </c>
-      <c r="D193" s="8" t="s">
+      <c r="D193" s="6" t="s">
         <v>754</v>
       </c>
-      <c r="E193" s="7" t="s">
+      <c r="E193" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F193" s="7" t="s">
+      <c r="F193" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="G193" s="7">
+      <c r="G193" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A194" s="7" t="s">
+    <row r="194" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A194" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="B194" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C194" s="8" t="s">
+      <c r="C194" s="6" t="s">
         <v>756</v>
       </c>
-      <c r="D194" s="8" t="s">
+      <c r="D194" s="6" t="s">
         <v>757</v>
       </c>
-      <c r="E194" s="7" t="s">
+      <c r="E194" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F194" s="7" t="s">
+      <c r="F194" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="G194" s="7">
+      <c r="G194" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A195" s="7" t="s">
+    <row r="195" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A195" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="B195" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C195" s="8" t="s">
+      <c r="C195" s="6" t="s">
         <v>759</v>
       </c>
-      <c r="D195" s="8" t="s">
+      <c r="D195" s="6" t="s">
         <v>760</v>
       </c>
-      <c r="E195" s="7" t="s">
+      <c r="E195" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="F195" s="7" t="s">
+      <c r="F195" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="G195" s="7">
+      <c r="G195" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A196" s="7" t="s">
+    <row r="196" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A196" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="B196" s="7" t="s">
+      <c r="B196" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C196" s="8" t="s">
+      <c r="C196" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="D196" s="8" t="s">
+      <c r="D196" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="E196" s="7" t="s">
+      <c r="E196" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="F196" s="7" t="s">
+      <c r="F196" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="G196" s="7">
+      <c r="G196" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A197" s="7" t="s">
+    <row r="197" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A197" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B197" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C197" s="8" t="s">
+      <c r="C197" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="D197" s="8" t="s">
+      <c r="D197" s="6" t="s">
         <v>769</v>
       </c>
-      <c r="E197" s="7" t="s">
+      <c r="E197" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="F197" s="7" t="s">
+      <c r="F197" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="G197" s="7">
+      <c r="G197" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A198" s="7" t="s">
+    <row r="198" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A198" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="B198" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C198" s="8" t="s">
+      <c r="C198" s="6" t="s">
         <v>772</v>
       </c>
-      <c r="D198" s="8" t="s">
+      <c r="D198" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="E198" s="7" t="s">
+      <c r="E198" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="F198" s="7" t="s">
+      <c r="F198" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="G198" s="7">
+      <c r="G198" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A199" s="7" t="s">
+    <row r="199" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A199" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B199" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C199" s="8" t="s">
+      <c r="C199" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="D199" s="8" t="s">
+      <c r="D199" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="E199" s="7" t="s">
+      <c r="E199" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="F199" s="7" t="s">
+      <c r="F199" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G199" s="7">
+      <c r="G199" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A200" s="7" t="s">
+    <row r="200" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A200" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="B200" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C200" s="8" t="s">
+      <c r="C200" s="6" t="s">
         <v>780</v>
       </c>
-      <c r="D200" s="8" t="s">
+      <c r="D200" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="E200" s="7" t="s">
+      <c r="E200" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="F200" s="7" t="s">
+      <c r="F200" s="5" t="s">
         <v>782</v>
       </c>
-      <c r="G200" s="7">
+      <c r="G200" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A201" s="7" t="s">
+    <row r="201" spans="1:7" ht="56" x14ac:dyDescent="0.2">
+      <c r="A201" s="5" t="s">
         <v>783</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B201" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C201" s="8" t="s">
+      <c r="C201" s="6" t="s">
         <v>784</v>
       </c>
-      <c r="D201" s="8" t="s">
+      <c r="D201" s="6" t="s">
         <v>785</v>
       </c>
-      <c r="E201" s="7" t="s">
+      <c r="E201" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="F201" s="7" t="s">
+      <c r="F201" s="5" t="s">
         <v>786</v>
       </c>
-      <c r="G201" s="7">
+      <c r="G201" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="A202" s="7" t="s">
+    <row r="202" spans="1:7" ht="70" x14ac:dyDescent="0.2">
+      <c r="A202" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="B202" s="7" t="s">
+      <c r="B202" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C202" s="8" t="s">
+      <c r="C202" s="6" t="s">
         <v>788</v>
       </c>
-      <c r="D202" s="8" t="s">
+      <c r="D202" s="6" t="s">
         <v>789</v>
       </c>
-      <c r="E202" s="7" t="s">
+      <c r="E202" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="F202" s="7" t="s">
+      <c r="F202" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="G202" s="7">
+      <c r="G202" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A203" s="7" t="s">
+    <row r="203" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A203" s="5" t="s">
         <v>790</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B203" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C203" s="8" t="s">
+      <c r="C203" s="6" t="s">
         <v>791</v>
       </c>
-      <c r="D203" s="8" t="s">
+      <c r="D203" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="E203" s="7" t="s">
+      <c r="E203" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="F203" s="7" t="s">
+      <c r="F203" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="G203" s="7">
+      <c r="G203" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A204" s="7" t="s">
+    <row r="204" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A204" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="B204" s="7" t="s">
+      <c r="B204" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C204" s="8" t="s">
+      <c r="C204" s="6" t="s">
         <v>796</v>
       </c>
-      <c r="D204" s="8" t="s">
+      <c r="D204" s="6" t="s">
         <v>797</v>
       </c>
-      <c r="E204" s="7" t="s">
+      <c r="E204" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="F204" s="7" t="s">
+      <c r="F204" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="G204" s="7">
+      <c r="G204" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A205" s="7" t="s">
+    <row r="205" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A205" s="5" t="s">
         <v>798</v>
       </c>
-      <c r="B205" s="7" t="s">
+      <c r="B205" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C205" s="8" t="s">
+      <c r="C205" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="D205" s="8" t="s">
+      <c r="D205" s="6" t="s">
         <v>800</v>
       </c>
-      <c r="E205" s="7" t="s">
+      <c r="E205" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="F205" s="7" t="s">
+      <c r="F205" s="5" t="s">
         <v>801</v>
       </c>
-      <c r="G205" s="7">
+      <c r="G205" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A206" s="7" t="s">
+    <row r="206" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A206" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="B206" s="7" t="s">
+      <c r="B206" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C206" s="8" t="s">
+      <c r="C206" s="6" t="s">
         <v>803</v>
       </c>
-      <c r="D206" s="8" t="s">
+      <c r="D206" s="6" t="s">
         <v>804</v>
       </c>
-      <c r="E206" s="7" t="s">
+      <c r="E206" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="F206" s="7" t="s">
+      <c r="F206" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="G206" s="7">
+      <c r="G206" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A207" s="7" t="s">
+    <row r="207" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A207" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="B207" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C207" s="8" t="s">
+      <c r="C207" s="6" t="s">
         <v>807</v>
       </c>
-      <c r="D207" s="8" t="s">
+      <c r="D207" s="6" t="s">
         <v>808</v>
       </c>
-      <c r="E207" s="7" t="s">
+      <c r="E207" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="F207" s="7" t="s">
+      <c r="F207" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="G207" s="7">
+      <c r="G207" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A208" s="7" t="s">
+    <row r="208" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A208" s="5" t="s">
         <v>810</v>
       </c>
-      <c r="B208" s="7" t="s">
+      <c r="B208" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C208" s="8" t="s">
+      <c r="C208" s="6" t="s">
         <v>811</v>
       </c>
-      <c r="D208" s="8" t="s">
+      <c r="D208" s="6" t="s">
         <v>812</v>
       </c>
-      <c r="E208" s="7" t="s">
+      <c r="E208" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="F208" s="7" t="s">
+      <c r="F208" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="G208" s="7">
+      <c r="G208" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A209" s="7" t="s">
+    <row r="209" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A209" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="B209" s="7" t="s">
+      <c r="B209" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C209" s="8" t="s">
+      <c r="C209" s="6" t="s">
         <v>815</v>
       </c>
-      <c r="D209" s="8" t="s">
+      <c r="D209" s="6" t="s">
         <v>816</v>
       </c>
-      <c r="E209" s="7" t="s">
+      <c r="E209" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="F209" s="7" t="s">
+      <c r="F209" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="G209" s="7">
+      <c r="G209" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A210" s="7" t="s">
+    <row r="210" spans="1:7" ht="126" x14ac:dyDescent="0.2">
+      <c r="A210" s="5" t="s">
         <v>818</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="B210" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C210" s="8" t="s">
+      <c r="C210" s="6" t="s">
         <v>819</v>
       </c>
-      <c r="D210" s="8" t="s">
+      <c r="D210" s="6" t="s">
         <v>820</v>
       </c>
-      <c r="E210" s="7" t="s">
+      <c r="E210" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="F210" s="7" t="s">
+      <c r="F210" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="G210" s="7">
+      <c r="G210" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A211" s="7" t="s">
+    <row r="211" spans="1:7" ht="98" x14ac:dyDescent="0.2">
+      <c r="A211" s="5" t="s">
         <v>821</v>
       </c>
-      <c r="B211" s="7" t="s">
+      <c r="B211" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C211" s="8" t="s">
+      <c r="C211" s="6" t="s">
         <v>822</v>
       </c>
-      <c r="D211" s="8" t="s">
+      <c r="D211" s="6" t="s">
         <v>823</v>
       </c>
-      <c r="E211" s="7" t="s">
+      <c r="E211" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="F211" s="7" t="s">
+      <c r="F211" s="5" t="s">
         <v>825</v>
       </c>
-      <c r="G211" s="7">
+      <c r="G211" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A212" s="7" t="s">
+    <row r="212" spans="1:7" ht="98" x14ac:dyDescent="0.2">
+      <c r="A212" s="5" t="s">
         <v>826</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B212" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C212" s="8" t="s">
+      <c r="C212" s="6" t="s">
         <v>827</v>
       </c>
-      <c r="D212" s="8" t="s">
+      <c r="D212" s="6" t="s">
         <v>828</v>
       </c>
-      <c r="E212" s="7" t="s">
+      <c r="E212" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="F212" s="7" t="s">
+      <c r="F212" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="G212" s="7">
+      <c r="G212" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A213" s="7" t="s">
+    <row r="213" spans="1:7" ht="98" x14ac:dyDescent="0.2">
+      <c r="A213" s="5" t="s">
         <v>830</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="B213" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C213" s="8" t="s">
+      <c r="C213" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="D213" s="8" t="s">
+      <c r="D213" s="6" t="s">
         <v>832</v>
       </c>
-      <c r="E213" s="7" t="s">
+      <c r="E213" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="F213" s="7" t="s">
+      <c r="F213" s="5" t="s">
         <v>833</v>
       </c>
-      <c r="G213" s="7">
+      <c r="G213" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A214" s="7" t="s">
+    <row r="214" spans="1:7" ht="98" x14ac:dyDescent="0.2">
+      <c r="A214" s="5" t="s">
         <v>834</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B214" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C214" s="8" t="s">
+      <c r="C214" s="6" t="s">
         <v>835</v>
       </c>
-      <c r="D214" s="8" t="s">
+      <c r="D214" s="6" t="s">
         <v>836</v>
       </c>
-      <c r="E214" s="7" t="s">
+      <c r="E214" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="F214" s="7" t="s">
+      <c r="F214" s="5" t="s">
         <v>837</v>
       </c>
-      <c r="G214" s="7">
+      <c r="G214" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A215" s="7" t="s">
+    <row r="215" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A215" s="5" t="s">
         <v>838</v>
       </c>
-      <c r="B215" s="7" t="s">
+      <c r="B215" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C215" s="8" t="s">
+      <c r="C215" s="6" t="s">
         <v>839</v>
       </c>
-      <c r="D215" s="8" t="s">
+      <c r="D215" s="6" t="s">
         <v>840</v>
       </c>
-      <c r="E215" s="7" t="s">
+      <c r="E215" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="F215" s="7" t="s">
+      <c r="F215" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="G215" s="7">
+      <c r="G215" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A216" s="7" t="s">
+    <row r="216" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A216" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="B216" s="7" t="s">
+      <c r="B216" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C216" s="8" t="s">
+      <c r="C216" s="6" t="s">
         <v>843</v>
       </c>
-      <c r="D216" s="8" t="s">
+      <c r="D216" s="6" t="s">
         <v>844</v>
       </c>
-      <c r="E216" s="7" t="s">
+      <c r="E216" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="F216" s="7" t="s">
+      <c r="F216" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="G216" s="7">
+      <c r="G216" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A217" s="7" t="s">
+    <row r="217" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A217" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="B217" s="7" t="s">
+      <c r="B217" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C217" s="8" t="s">
+      <c r="C217" s="6" t="s">
         <v>846</v>
       </c>
-      <c r="D217" s="8" t="s">
+      <c r="D217" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="E217" s="7" t="s">
+      <c r="E217" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="F217" s="7" t="s">
+      <c r="F217" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="G217" s="7">
+      <c r="G217" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A218" s="7" t="s">
+    <row r="218" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A218" s="5" t="s">
         <v>849</v>
       </c>
-      <c r="B218" s="7" t="s">
+      <c r="B218" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C218" s="8" t="s">
+      <c r="C218" s="6" t="s">
         <v>850</v>
       </c>
-      <c r="D218" s="8" t="s">
+      <c r="D218" s="6" t="s">
         <v>851</v>
       </c>
-      <c r="E218" s="7" t="s">
+      <c r="E218" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="F218" s="7" t="s">
+      <c r="F218" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="G218" s="7">
+      <c r="G218" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A219" s="7" t="s">
+    <row r="219" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A219" s="5" t="s">
         <v>852</v>
       </c>
-      <c r="B219" s="7" t="s">
+      <c r="B219" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C219" s="8" t="s">
+      <c r="C219" s="6" t="s">
         <v>853</v>
       </c>
-      <c r="D219" s="8" t="s">
+      <c r="D219" s="6" t="s">
         <v>854</v>
       </c>
-      <c r="E219" s="7" t="s">
+      <c r="E219" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="F219" s="7" t="s">
+      <c r="F219" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="G219" s="7">
+      <c r="G219" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A220" s="7" t="s">
+    <row r="220" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A220" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B220" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C220" s="8" t="s">
+      <c r="C220" s="6" t="s">
         <v>857</v>
       </c>
-      <c r="D220" s="8" t="s">
+      <c r="D220" s="6" t="s">
         <v>858</v>
       </c>
-      <c r="E220" s="7" t="s">
+      <c r="E220" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="F220" s="7" t="s">
+      <c r="F220" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="G220" s="7">
+      <c r="G220" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A221" s="7" t="s">
+    <row r="221" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A221" s="5" t="s">
         <v>859</v>
       </c>
-      <c r="B221" s="7" t="s">
+      <c r="B221" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C221" s="8" t="s">
+      <c r="C221" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="D221" s="8" t="s">
+      <c r="D221" s="6" t="s">
         <v>861</v>
       </c>
-      <c r="E221" s="7" t="s">
+      <c r="E221" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="F221" s="7" t="s">
+      <c r="F221" s="5" t="s">
         <v>862</v>
       </c>
-      <c r="G221" s="7">
+      <c r="G221" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A222" s="7" t="s">
+    <row r="222" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A222" s="5" t="s">
         <v>863</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B222" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C222" s="8" t="s">
+      <c r="C222" s="6" t="s">
         <v>864</v>
       </c>
-      <c r="D222" s="8" t="s">
+      <c r="D222" s="6" t="s">
         <v>865</v>
       </c>
-      <c r="E222" s="7" t="s">
+      <c r="E222" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="F222" s="7" t="s">
+      <c r="F222" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="G222" s="7">
+      <c r="G222" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A223" s="7" t="s">
+    <row r="223" spans="1:7" ht="98" x14ac:dyDescent="0.2">
+      <c r="A223" s="5" t="s">
         <v>866</v>
       </c>
-      <c r="B223" s="7" t="s">
+      <c r="B223" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C223" s="8" t="s">
+      <c r="C223" s="6" t="s">
         <v>867</v>
       </c>
-      <c r="D223" s="8" t="s">
+      <c r="D223" s="6" t="s">
         <v>868</v>
       </c>
-      <c r="E223" s="7" t="s">
+      <c r="E223" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="F223" s="7" t="s">
+      <c r="F223" s="5" t="s">
         <v>870</v>
       </c>
-      <c r="G223" s="7">
+      <c r="G223" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A224" s="7" t="s">
+    <row r="224" spans="1:7" ht="98" x14ac:dyDescent="0.2">
+      <c r="A224" s="5" t="s">
         <v>871</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B224" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C224" s="8" t="s">
+      <c r="C224" s="6" t="s">
         <v>872</v>
       </c>
-      <c r="D224" s="8" t="s">
+      <c r="D224" s="6" t="s">
         <v>873</v>
       </c>
-      <c r="E224" s="7" t="s">
+      <c r="E224" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="F224" s="7" t="s">
+      <c r="F224" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="G224" s="7">
+      <c r="G224" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A225" s="7" t="s">
+    <row r="225" spans="1:7" ht="98" x14ac:dyDescent="0.2">
+      <c r="A225" s="5" t="s">
         <v>874</v>
       </c>
-      <c r="B225" s="7" t="s">
+      <c r="B225" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C225" s="8" t="s">
+      <c r="C225" s="6" t="s">
         <v>875</v>
       </c>
-      <c r="D225" s="8" t="s">
+      <c r="D225" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="E225" s="7" t="s">
+      <c r="E225" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="F225" s="7" t="s">
+      <c r="F225" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="G225" s="7">
+      <c r="G225" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A226" s="7" t="s">
+    <row r="226" spans="1:7" ht="98" x14ac:dyDescent="0.2">
+      <c r="A226" s="5" t="s">
         <v>877</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C226" s="8" t="s">
+      <c r="C226" s="6" t="s">
         <v>878</v>
       </c>
-      <c r="D226" s="8" t="s">
+      <c r="D226" s="6" t="s">
         <v>879</v>
       </c>
-      <c r="E226" s="7" t="s">
+      <c r="E226" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="F226" s="7" t="s">
+      <c r="F226" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="G226" s="7">
+      <c r="G226" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A227" s="7" t="s">
+    <row r="227" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A227" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="B227" s="7" t="s">
+      <c r="B227" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C227" s="8" t="s">
+      <c r="C227" s="6" t="s">
         <v>881</v>
       </c>
-      <c r="D227" s="8" t="s">
+      <c r="D227" s="6" t="s">
         <v>882</v>
       </c>
-      <c r="E227" s="7" t="s">
+      <c r="E227" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="F227" s="7" t="s">
+      <c r="F227" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="G227" s="7">
+      <c r="G227" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A228" s="7" t="s">
+    <row r="228" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A228" s="5" t="s">
         <v>883</v>
       </c>
-      <c r="B228" s="7" t="s">
+      <c r="B228" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C228" s="8" t="s">
+      <c r="C228" s="6" t="s">
         <v>884</v>
       </c>
-      <c r="D228" s="8" t="s">
+      <c r="D228" s="6" t="s">
         <v>885</v>
       </c>
-      <c r="E228" s="7" t="s">
+      <c r="E228" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="F228" s="7" t="s">
+      <c r="F228" s="5" t="s">
         <v>886</v>
       </c>
-      <c r="G228" s="7">
+      <c r="G228" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A229" s="7" t="s">
+    <row r="229" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A229" s="5" t="s">
         <v>887</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B229" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C229" s="8" t="s">
+      <c r="C229" s="6" t="s">
         <v>888</v>
       </c>
-      <c r="D229" s="8" t="s">
+      <c r="D229" s="6" t="s">
         <v>889</v>
       </c>
-      <c r="E229" s="7" t="s">
+      <c r="E229" s="5" t="s">
         <v>890</v>
       </c>
-      <c r="F229" s="7" t="s">
+      <c r="F229" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="G229" s="7">
+      <c r="G229" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A230" s="7" t="s">
+    <row r="230" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A230" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B230" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C230" s="8" t="s">
+      <c r="C230" s="6" t="s">
         <v>892</v>
       </c>
-      <c r="D230" s="8" t="s">
+      <c r="D230" s="6" t="s">
         <v>893</v>
       </c>
-      <c r="E230" s="7" t="s">
+      <c r="E230" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="F230" s="7" t="s">
+      <c r="F230" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="G230" s="7">
+      <c r="G230" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A231" s="7" t="s">
+    <row r="231" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A231" s="5" t="s">
         <v>894</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C231" s="8" t="s">
+      <c r="C231" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="D231" s="8" t="s">
+      <c r="D231" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="E231" s="7" t="s">
+      <c r="E231" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="F231" s="7" t="s">
+      <c r="F231" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="G231" s="7">
+      <c r="G231" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A232" s="7" t="s">
+    <row r="232" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A232" s="5" t="s">
         <v>897</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B232" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C232" s="8" t="s">
+      <c r="C232" s="6" t="s">
         <v>898</v>
       </c>
-      <c r="D232" s="8" t="s">
+      <c r="D232" s="6" t="s">
         <v>899</v>
       </c>
-      <c r="E232" s="7" t="s">
+      <c r="E232" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="F232" s="7" t="s">
+      <c r="F232" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="G232" s="7">
+      <c r="G232" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A233" s="7" t="s">
+    <row r="233" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A233" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C233" s="8" t="s">
+      <c r="C233" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="D233" s="8" t="s">
+      <c r="D233" s="6" t="s">
         <v>902</v>
       </c>
-      <c r="E233" s="7" t="s">
+      <c r="E233" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="F233" s="7" t="s">
+      <c r="F233" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="G233" s="7">
+      <c r="G233" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A234" s="7" t="s">
+    <row r="234" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A234" s="5" t="s">
         <v>903</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C234" s="8" t="s">
+      <c r="C234" s="6" t="s">
         <v>904</v>
       </c>
-      <c r="D234" s="8" t="s">
+      <c r="D234" s="6" t="s">
         <v>905</v>
       </c>
-      <c r="E234" s="7" t="s">
+      <c r="E234" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="F234" s="7" t="s">
+      <c r="F234" s="5" t="s">
         <v>906</v>
       </c>
-      <c r="G234" s="7">
+      <c r="G234" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A235" s="7" t="s">
+    <row r="235" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A235" s="5" t="s">
         <v>907</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C235" s="8" t="s">
+      <c r="C235" s="6" t="s">
         <v>908</v>
       </c>
-      <c r="D235" s="8" t="s">
+      <c r="D235" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="E235" s="7" t="s">
+      <c r="E235" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="F235" s="7" t="s">
+      <c r="F235" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="G235" s="7">
+      <c r="G235" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A236" s="7" t="s">
+    <row r="236" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A236" s="5" t="s">
         <v>911</v>
       </c>
-      <c r="B236" s="7" t="s">
+      <c r="B236" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C236" s="8" t="s">
+      <c r="C236" s="6" t="s">
         <v>912</v>
       </c>
-      <c r="D236" s="8" t="s">
+      <c r="D236" s="6" t="s">
         <v>913</v>
       </c>
-      <c r="E236" s="7" t="s">
+      <c r="E236" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="F236" s="7" t="s">
+      <c r="F236" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="G236" s="7">
+      <c r="G236" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A237" s="7" t="s">
+    <row r="237" spans="1:7" ht="42" x14ac:dyDescent="0.2">
+      <c r="A237" s="5" t="s">
         <v>914</v>
       </c>
-      <c r="B237" s="7" t="s">
+      <c r="B237" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C237" s="8" t="s">
+      <c r="C237" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="D237" s="8" t="s">
+      <c r="D237" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="E237" s="7" t="s">
+      <c r="E237" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="F237" s="7" t="s">
+      <c r="F237" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="G237" s="7">
+      <c r="G237" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A238" s="7" t="s">
+    <row r="238" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A238" s="5" t="s">
         <v>917</v>
       </c>
-      <c r="B238" s="7" t="s">
+      <c r="B238" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C238" s="8" t="s">
+      <c r="C238" s="6" t="s">
         <v>904</v>
       </c>
-      <c r="D238" s="8" t="s">
+      <c r="D238" s="6" t="s">
         <v>918</v>
       </c>
-      <c r="E238" s="7" t="s">
+      <c r="E238" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="F238" s="7" t="s">
+      <c r="F238" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="G238" s="7">
+      <c r="G238" s="5">
         <v>2</v>
       </c>
     </row>
